--- a/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
+++ b/results/models/summary_all_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
@@ -536,28 +536,28 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.056</v>
+        <v>0.061</v>
       </c>
       <c r="I2" t="n">
-        <v>19.4018</v>
+        <v>35.4943</v>
       </c>
       <c r="J2" t="n">
-        <v>16.9238</v>
+        <v>33.3005</v>
       </c>
       <c r="K2" t="n">
-        <v>8.260199999999999</v>
+        <v>7.3125</v>
       </c>
       <c r="L2" t="n">
-        <v>16.9238</v>
+        <v>33.3005</v>
       </c>
       <c r="M2" t="n">
-        <v>1.8672</v>
+        <v>1.9076</v>
       </c>
       <c r="N2" t="n">
-        <v>6.0644</v>
+        <v>6.1768</v>
       </c>
       <c r="O2" t="n">
-        <v>3.7004</v>
+        <v>3.8857</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -599,28 +599,28 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.042</v>
+        <v>0.045</v>
       </c>
       <c r="I3" t="n">
-        <v>19.3898</v>
+        <v>35.4922</v>
       </c>
       <c r="J3" t="n">
-        <v>16.9238</v>
+        <v>33.1525</v>
       </c>
       <c r="K3" t="n">
-        <v>8.2201</v>
+        <v>7.799</v>
       </c>
       <c r="L3" t="n">
-        <v>16.9238</v>
+        <v>33.1525</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8672</v>
+        <v>1.405</v>
       </c>
       <c r="N3" t="n">
-        <v>6.0644</v>
+        <v>6.6268</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7004</v>
+        <v>3.9601</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -662,28 +662,28 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="I4" t="n">
-        <v>19.5715</v>
+        <v>35.6778</v>
       </c>
       <c r="J4" t="n">
-        <v>16.6561</v>
+        <v>33.1189</v>
       </c>
       <c r="K4" t="n">
-        <v>9.7178</v>
+        <v>8.5298</v>
       </c>
       <c r="L4" t="n">
-        <v>16.6561</v>
+        <v>33.1189</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9357</v>
+        <v>1.5844</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1899</v>
+        <v>6.3507</v>
       </c>
       <c r="O4" t="n">
-        <v>3.6739</v>
+        <v>3.8727</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -725,28 +725,28 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>20.5987</v>
+        <v>36.7672</v>
       </c>
       <c r="J5" t="n">
-        <v>16.7431</v>
+        <v>33.0982</v>
       </c>
       <c r="K5" t="n">
-        <v>12.8521</v>
+        <v>12.2299</v>
       </c>
       <c r="L5" t="n">
-        <v>16.7431</v>
+        <v>33.0982</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4778</v>
+        <v>1.5844</v>
       </c>
       <c r="N5" t="n">
-        <v>5.9527</v>
+        <v>5.9346</v>
       </c>
       <c r="O5" t="n">
-        <v>3.6896</v>
+        <v>3.9156</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -788,28 +788,28 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="I6" t="n">
-        <v>20.502</v>
+        <v>36.6608</v>
       </c>
       <c r="J6" t="n">
-        <v>16.8527</v>
+        <v>33.3005</v>
       </c>
       <c r="K6" t="n">
-        <v>12.1642</v>
+        <v>11.2011</v>
       </c>
       <c r="L6" t="n">
-        <v>16.8527</v>
+        <v>33.3005</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4778</v>
+        <v>1.9076</v>
       </c>
       <c r="N6" t="n">
-        <v>6.0644</v>
+        <v>6.1768</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7199</v>
+        <v>3.8857</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -851,28 +851,28 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.047</v>
+        <v>0.041</v>
       </c>
       <c r="I7" t="n">
-        <v>20.8661</v>
+        <v>36.9875</v>
       </c>
       <c r="J7" t="n">
-        <v>16.5162</v>
+        <v>33.1189</v>
       </c>
       <c r="K7" t="n">
-        <v>14.4996</v>
+        <v>12.8954</v>
       </c>
       <c r="L7" t="n">
-        <v>16.5162</v>
+        <v>33.1189</v>
       </c>
       <c r="M7" t="n">
-        <v>1.8205</v>
+        <v>1.5844</v>
       </c>
       <c r="N7" t="n">
-        <v>5.9324</v>
+        <v>6.3507</v>
       </c>
       <c r="O7" t="n">
-        <v>3.6686</v>
+        <v>3.8727</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -914,28 +914,28 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.045</v>
+        <v>0.041</v>
       </c>
       <c r="I8" t="n">
-        <v>19.7519</v>
+        <v>35.7986</v>
       </c>
       <c r="J8" t="n">
-        <v>16.9574</v>
+        <v>33.1889</v>
       </c>
       <c r="K8" t="n">
-        <v>9.315</v>
+        <v>8.6989</v>
       </c>
       <c r="L8" t="n">
-        <v>16.9574</v>
+        <v>33.1889</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8205</v>
+        <v>1.7128</v>
       </c>
       <c r="N8" t="n">
-        <v>6.0024</v>
+        <v>6.1932</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6962</v>
+        <v>3.9171</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -977,28 +977,28 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.049</v>
+        <v>0.042</v>
       </c>
       <c r="I9" t="n">
-        <v>19.7255</v>
+        <v>35.8072</v>
       </c>
       <c r="J9" t="n">
-        <v>17.0047</v>
+        <v>33.1525</v>
       </c>
       <c r="K9" t="n">
-        <v>9.0694</v>
+        <v>8.849</v>
       </c>
       <c r="L9" t="n">
-        <v>17.0047</v>
+        <v>33.1525</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8672</v>
+        <v>1.405</v>
       </c>
       <c r="N9" t="n">
-        <v>6.0329</v>
+        <v>6.6268</v>
       </c>
       <c r="O9" t="n">
-        <v>3.7127</v>
+        <v>3.9601</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1040,28 +1040,28 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.045</v>
+        <v>0.043</v>
       </c>
       <c r="I10" t="n">
-        <v>20.8653</v>
+        <v>36.8201</v>
       </c>
       <c r="J10" t="n">
-        <v>16.405</v>
+        <v>33.1189</v>
       </c>
       <c r="K10" t="n">
-        <v>14.8676</v>
+        <v>12.3375</v>
       </c>
       <c r="L10" t="n">
-        <v>16.405</v>
+        <v>33.1189</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8205</v>
+        <v>1.5844</v>
       </c>
       <c r="N10" t="n">
-        <v>5.3331</v>
+        <v>6.3507</v>
       </c>
       <c r="O10" t="n">
-        <v>3.641</v>
+        <v>3.8727</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1103,28 +1103,28 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.049</v>
+        <v>0.044</v>
       </c>
       <c r="I11" t="n">
-        <v>20.7979</v>
+        <v>36.9951</v>
       </c>
       <c r="J11" t="n">
-        <v>16.8527</v>
+        <v>33.1984</v>
       </c>
       <c r="K11" t="n">
-        <v>13.1506</v>
+        <v>12.6555</v>
       </c>
       <c r="L11" t="n">
-        <v>16.8527</v>
+        <v>33.1984</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4778</v>
+        <v>1.9076</v>
       </c>
       <c r="N11" t="n">
-        <v>6.0644</v>
+        <v>5.9109</v>
       </c>
       <c r="O11" t="n">
-        <v>3.7199</v>
+        <v>3.873</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1166,28 +1166,28 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="I12" t="n">
-        <v>20.7698</v>
+        <v>36.9607</v>
       </c>
       <c r="J12" t="n">
-        <v>16.9238</v>
+        <v>33.3005</v>
       </c>
       <c r="K12" t="n">
-        <v>12.8199</v>
+        <v>12.2007</v>
       </c>
       <c r="L12" t="n">
-        <v>16.9238</v>
+        <v>33.3005</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8672</v>
+        <v>1.9076</v>
       </c>
       <c r="N12" t="n">
-        <v>6.0644</v>
+        <v>6.1768</v>
       </c>
       <c r="O12" t="n">
-        <v>3.7004</v>
+        <v>3.8857</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -1229,28 +1229,28 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="I13" t="n">
-        <v>20.9243</v>
+        <v>37.0799</v>
       </c>
       <c r="J13" t="n">
-        <v>16.6089</v>
+        <v>33.1189</v>
       </c>
       <c r="K13" t="n">
-        <v>14.3848</v>
+        <v>13.2033</v>
       </c>
       <c r="L13" t="n">
-        <v>16.6089</v>
+        <v>33.1189</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8205</v>
+        <v>1.5844</v>
       </c>
       <c r="N13" t="n">
-        <v>5.1899</v>
+        <v>6.3507</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6573</v>
+        <v>3.8727</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
